--- a/output/reports/cv_experiment_DecisionTree_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.601670265197754</v>
+        <v>0.1527729034423828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998197420785205</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998082929272684</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>2.463835082580447</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>1.380322209436134</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.05957293510437</v>
+        <v>0.1110231876373291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9998312293752214</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998082929272684</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>2.463835082580447</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>1.380322209436134</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.14639353752136</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9998324116003632</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9998082929272684</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.463835082580447</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.380322209436134</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22.16533970832825</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9998233887052492</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9998082929272684</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.463835082580447</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.380322209436134</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.601670265197754</v>
+        <v>0.1527729034423828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998197420785205</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998082929272684</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>2.463835082580447</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>1.380322209436134</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.05957293510437</v>
+        <v>0.1110231876373291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9998312293752214</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998082929272684</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>2.463835082580447</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>1.380322209436134</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.14639353752136</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9998324116003632</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9998082929272684</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.463835082580447</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.380322209436134</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22.16533970832825</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9998233887052492</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9998082929272684</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.463835082580447</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.380322209436134</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
